--- a/NuevaData/Presentacion/Investigacion/FACTOR 6. PERMANENCIA Y GRADUACIÓN/d. Seguimiento al avance de trabajos de grado y tiempos de permanencia/F6_Permanencia_y_Graduacion_Investigacion.xlsx
+++ b/NuevaData/Presentacion/Investigacion/FACTOR 6. PERMANENCIA Y GRADUACIÓN/d. Seguimiento al avance de trabajos de grado y tiempos de permanencia/F6_Permanencia_y_Graduacion_Investigacion.xlsx
@@ -745,13 +745,13 @@
         <v>18</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Solicitudes por ronda: 1.ª = 21, 2.ª = 4, 3.ª = 2. Una estudiante radicó en dos rondas y cuenta una sola vez entre los estudiantes distintos. Modalidad: la del cuadro de la coordinación («Estudiantes Prórroga 2026-3»), contrastada con Cóndor y las bases MCIC (hoja «Cruces y alertas»). Graduados: año estimado por la última matrícula en Cóndor; «Sin modalidad registrada» agrupa graduados del plan anterior (proyectos 195–495).</t>
+          <t>Solicitudes por ronda: 1.ª = 21, 2.ª = 4, 3.ª = 2. Una estudiante radicó en dos rondas y cuenta una sola vez entre los estudiantes distintos. Modalidad: la del cuadro de la coordinación («Estudiantes Prórroga 2026-3»), contrastada con Cóndor y las bases MCIC (hoja «Cruces y alertas»). Graduados: año estimado por la última matrícula en Cóndor;  Investigación incluye a los graduados del plan anterior (proyectos 95–495).</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5372,47 +5372,22 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>5</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Sin modalidad registrada</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>25</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/NuevaData/Presentacion/Investigacion/FACTOR 6. PERMANENCIA Y GRADUACIÓN/d. Seguimiento al avance de trabajos de grado y tiempos de permanencia/F6_Permanencia_y_Graduacion_Investigacion.xlsx
+++ b/NuevaData/Presentacion/Investigacion/FACTOR 6. PERMANENCIA Y GRADUACIÓN/d. Seguimiento al avance de trabajos de grado y tiempos de permanencia/F6_Permanencia_y_Graduacion_Investigacion.xlsx
@@ -12,12 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAGOT" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seguimiento PAGOT 2026-3" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normativa PAGOT" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cruces y alertas" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acompañamiento" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graduados" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acompañamiento" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graduados" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Solicitudes de prórroga'!$A$4:$N$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Solicitudes de prórroga'!$A$4:$M$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Seguimiento PAGOT 2026-3'!$A$4:$P$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Normativa PAGOT'!$A$4:$E$13</definedName>
   </definedNames>
@@ -28,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,18 +77,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="004B5563"/>
-      <sz val="9.5"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <color rgb="001F5FA8"/>
       <sz val="10"/>
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -104,11 +97,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCE6F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF4E5"/>
       </patternFill>
     </fill>
     <fill>
@@ -187,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -208,19 +196,16 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -588,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -679,17 +664,17 @@
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Solicitudes de prórroga 2026-3</t>
+          <t>Solicitudes de prórroga radicadas 2026-3</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Estudiantes distintos</t>
+          <t>Estudiantes que solicitaron prórroga</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>De ellos, PAGOT</t>
+          <t>Solicitantes que son PAGOT</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -715,7 +700,7 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>PAGOT con pago 2026-3</t>
+          <t>PAGOT que pagaron la matrícula 2026-3</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -736,7 +721,7 @@
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>30</v>
@@ -748,15 +733,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Solicitudes por ronda: 1.ª = 21, 2.ª = 4, 3.ª = 2. Una estudiante radicó en dos rondas y cuenta una sola vez entre los estudiantes distintos. Modalidad: la del cuadro de la coordinación («Estudiantes Prórroga 2026-3»), contrastada con Cóndor y las bases MCIC (hoja «Cruces y alertas»). Graduados: año estimado por la última matrícula en Cóndor;  Investigación incluye a los graduados del plan anterior (proyectos 95–495).</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="25">
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A1:H1"/>
@@ -765,7 +743,6 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A16:H16"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="G13:H13"/>
@@ -810,7 +787,6 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
     <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -828,74 +804,69 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Ronda</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Fecha del correo</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Modalidad</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Énfasis</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Tipo de estudiante</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Aval anteproyecto</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Fecha del aval</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>Componente 1 (evento o revista)</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>Tesis radicada</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>Créditos aprobados</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>Trabajo de grado</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>Estado en Cóndor</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="inlineStr">
-        <is>
-          <t>Observación</t>
         </is>
       </c>
     </row>
@@ -963,73 +934,71 @@
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>P1-04</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>1.ª</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Ingeniería de Software</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>PAGOT</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>31/10/2025</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>Congreso LoHacemosxTIC2026</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO 1</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr">
+      <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1095,73 +1064,71 @@
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>P1-07</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>1.ª</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Teleinformática</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>PAGOT</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>03/09/2025</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>Congreso LoHacemosxTIC2026</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K8" s="12" t="n">
+      <c r="K8" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="L8" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO 1</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr">
+      <c r="M8" s="11" t="inlineStr">
         <is>
           <t>En renovación de matrícula - Vacaciones (última matrícula 2026-1)</t>
         </is>
       </c>
-      <c r="N8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1227,73 +1194,71 @@
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>P1-09</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>1.ª</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Ingeniería de Software</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>PAGOT</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>23/05/2025</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Congreso LoHacemosxTIC2026</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K10" s="12" t="n">
+      <c r="K10" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO 1</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1359,73 +1324,71 @@
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>P1-12</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>1.ª</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Teleinformática</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>24/10/2024</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>Congreso LoHacemosxTIC2026</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="K12" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="L12" s="12" t="inlineStr">
+      <c r="L12" s="11" t="inlineStr">
         <is>
           <t>TESIS 1</t>
         </is>
       </c>
-      <c r="M12" s="12" t="inlineStr">
+      <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1491,73 +1454,71 @@
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>P1-14</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>1.ª</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Teleinformática</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>PAGOT</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>03/09/2025</t>
         </is>
       </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>Congreso LoHacemosxTIC2026</t>
         </is>
       </c>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="K14" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="L14" s="12" t="inlineStr">
+      <c r="L14" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO 1</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr">
+      <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1623,73 +1584,71 @@
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>P1-17</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>1.ª</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Teleinformática</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>PAGOT</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>20/11/2025</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I16" s="11" t="inlineStr">
         <is>
           <t>Congreso LoHacemosxTIC2026</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="K16" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="L16" s="12" t="inlineStr">
+      <c r="L16" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO 1</t>
         </is>
       </c>
-      <c r="M16" s="12" t="inlineStr">
+      <c r="M16" s="11" t="inlineStr">
         <is>
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1755,73 +1714,71 @@
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>P1-19</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>1.ª</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Teleinformática</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>Sumisión de artículo a revista: "MDPI"</t>
         </is>
       </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="K18" s="11" t="n">
         <v>44</v>
       </c>
-      <c r="L18" s="12" t="inlineStr">
+      <c r="L18" s="11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M18" s="12" t="inlineStr">
+      <c r="M18" s="11" t="inlineStr">
         <is>
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1887,73 +1844,71 @@
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>P1-22</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>1.ª</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Ingeniería de Software</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>05/12/2025</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>Sumisión de artículo a revista: "Data Intelligence"</t>
         </is>
       </c>
-      <c r="J20" s="12" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="K20" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="L20" s="12" t="inlineStr">
+      <c r="L20" s="11" t="inlineStr">
         <is>
           <t>TESIS 1</t>
         </is>
       </c>
-      <c r="M20" s="12" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr">
         <is>
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -2019,73 +1974,71 @@
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>P1-24</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>1.ª</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Teleinformática</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>03/03/2026</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>Congreso LoHacemosxTIC2026</t>
         </is>
       </c>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="K22" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="L22" s="12" t="inlineStr">
+      <c r="L22" s="11" t="inlineStr">
         <is>
           <t>TESIS 1</t>
         </is>
       </c>
-      <c r="M22" s="12" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr">
         <is>
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -2151,75 +2104,69 @@
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>P1-26</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>1.ª</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Teleinformática</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>XXII Congreso Virtual en Inteligencia Artificial, Nutrición y Entrenamiento</t>
         </is>
       </c>
-      <c r="J24" s="12" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="K24" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="L24" s="12" t="inlineStr">
+      <c r="L24" s="11" t="inlineStr">
         <is>
           <t>TESIS 1 Le falta cursar 2 electivas</t>
         </is>
       </c>
-      <c r="M24" s="12" t="inlineStr">
+      <c r="M24" s="11" t="inlineStr">
         <is>
           <t>Matriculado (última matrícula 2026-3)</t>
-        </is>
-      </c>
-      <c r="N24" s="12" t="inlineStr">
-        <is>
-          <t>Sin correo de radicación en la carpeta CORREOS.</t>
         </is>
       </c>
     </row>
@@ -2287,77 +2234,71 @@
           <t>En renovación de matrícula - Vacaciones (última matrícula 2026-1)</t>
         </is>
       </c>
-      <c r="N25" s="6" t="inlineStr">
-        <is>
-          <t>Sin correo de radicación en la carpeta CORREOS.</t>
-        </is>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>P2-02</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>2.ª</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Ingeniería de Software</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>Congreso LoHacemosxTIC2026</t>
         </is>
       </c>
-      <c r="J26" s="12" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="K26" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="L26" s="11" t="inlineStr">
         <is>
           <t>TESIS 1</t>
         </is>
       </c>
-      <c r="M26" s="12" t="inlineStr">
+      <c r="M26" s="11" t="inlineStr">
         <is>
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -2423,73 +2364,71 @@
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>P2-05</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>2.ª</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Geomática</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>PAGOT</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>17/10/2015</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>Congreso Internacional en Ingeniería, Tecnología e Innovación – CIITI2026</t>
         </is>
       </c>
-      <c r="J28" s="12" t="inlineStr">
+      <c r="J28" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="K28" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="L28" s="12" t="inlineStr">
+      <c r="L28" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO 1</t>
         </is>
       </c>
-      <c r="M28" s="12" t="inlineStr">
+      <c r="M28" s="11" t="inlineStr">
         <is>
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N28" s="12" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -2555,73 +2494,71 @@
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>P3-01</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>3.ª</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Geomática</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>PAGOT</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>17/10/2025</t>
         </is>
       </c>
-      <c r="I30" s="12" t="inlineStr">
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>Congreso Internacional en Ingeniería, Tecnología e Innovación – CIITI2026</t>
         </is>
       </c>
-      <c r="J30" s="12" t="inlineStr">
+      <c r="J30" s="11" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="K30" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="L30" s="12" t="inlineStr">
+      <c r="L30" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO 1</t>
         </is>
       </c>
-      <c r="M30" s="12" t="inlineStr">
+      <c r="M30" s="11" t="inlineStr">
         <is>
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -2687,10 +2624,9 @@
           <t>Matriculado (última matrícula 2026-3)</t>
         </is>
       </c>
-      <c r="N31" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N31"/>
+  <autoFilter ref="A4:M31"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2736,22 +2672,22 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Estudiantes</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>También en seguimiento 2026-3</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>También solicitó prórroga 2026-3</t>
         </is>
@@ -2774,18 +2710,18 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Inscritos oficiales a PAGOT 2024-1 a 2025-3 (listado de aspirantes)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="11" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2806,18 +2742,18 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  de ellos, con pago registrado para 2026-3</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="D9" s="12" t="n">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    de ellos, pagaron la matrícula 2026-3 (recibo activo)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2845,12 +2781,12 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Estudiantes</t>
         </is>
@@ -2867,12 +2803,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Acta pendiente o no enviada</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2887,12 +2823,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Otra respuesta</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2904,12 +2840,12 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Estudiantes</t>
         </is>
@@ -2926,12 +2862,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Sin dato de estado</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2946,12 +2882,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Pérdida de calidad de estudiante - Suspendido</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2963,12 +2899,12 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Estudiantes</t>
         </is>
@@ -2985,12 +2921,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>2025-1</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="11" t="n">
         <v>22</v>
       </c>
     </row>
@@ -3059,82 +2995,82 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Énfasis (plan de ingreso)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Último periodo activo</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Créditos aprobados</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Periodos</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Matrículas</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Respuesta a la convocatoria</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Pago 2026-3</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>Plan 2026-3</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>Plan 2027-1</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>Plan 2027-3</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>Estado en Cóndor</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>Último recibo</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>Solicitó prórroga 2026-3</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="10" t="inlineStr">
         <is>
           <t>En base MCIC como PAGOT</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr">
+      <c r="P4" s="10" t="inlineStr">
         <is>
           <t>Inscrito oficial PAGOT</t>
         </is>
@@ -3217,76 +3153,76 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>G-02</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Teleinformática</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>2020-1</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Aceptó</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>SEMINARIO</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO I</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr">
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO II</t>
         </is>
       </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>En renovación de matrícula - Vacaciones</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr">
+      <c r="M6" s="11" t="inlineStr">
         <is>
           <t>2026-3 A</t>
         </is>
       </c>
-      <c r="N6" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O6" s="12" t="inlineStr">
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P6" s="12" t="inlineStr">
+      <c r="P6" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -3369,76 +3305,76 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>G-04</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Geomática</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>2021-3</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Acta pendiente o no enviada</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="L8" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr">
+      <c r="M8" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N8" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O8" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P8" s="12" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P8" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3521,76 +3457,76 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>G-06</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Ingeniería de Software</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>2021-3 *</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Aceptó</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>SEMINARIO</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO I</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO II</t>
         </is>
       </c>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>En renovación de matrícula - Vacaciones</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>2026-3 A</t>
         </is>
       </c>
-      <c r="N10" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O10" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P10" s="12" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P10" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3673,76 +3609,76 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>G-08</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Teleinformática</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Aceptó</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K12" s="12" t="inlineStr">
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L12" s="12" t="inlineStr">
+      <c r="L12" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M12" s="12" t="inlineStr">
+      <c r="M12" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N12" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O12" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P12" s="12" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O12" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -3780,121 +3716,121 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Pérdida de calidad de estudiante - Suspendido</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>2025-3 A</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>Pérdida de calidad de estudiante - Suspendido</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>2025-3 A</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O13" s="6" t="inlineStr">
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>G-10</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Ingeniería de Software</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>2023-3</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>Aceptó</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>G-10</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>2023-3</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>SEMINARIO</t>
         </is>
       </c>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO I / COMPUTACIÓN PARALELA</t>
         </is>
       </c>
-      <c r="K14" s="12" t="inlineStr">
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO II</t>
         </is>
       </c>
-      <c r="L14" s="12" t="inlineStr">
+      <c r="L14" s="11" t="inlineStr">
         <is>
           <t>Matriculado</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr">
+      <c r="M14" s="11" t="inlineStr">
         <is>
           <t>2026-3 A</t>
         </is>
       </c>
-      <c r="N14" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P14" s="12" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3977,76 +3913,76 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>G-12</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Ingeniería de Software</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>2024-1</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>Aceptó</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I16" s="11" t="inlineStr">
         <is>
           <t>SEMINARIO</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO I</t>
         </is>
       </c>
-      <c r="K16" s="12" t="inlineStr">
+      <c r="K16" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO II</t>
         </is>
       </c>
-      <c r="L16" s="12" t="inlineStr">
+      <c r="L16" s="11" t="inlineStr">
         <is>
           <t>Matriculado</t>
         </is>
       </c>
-      <c r="M16" s="12" t="inlineStr">
+      <c r="M16" s="11" t="inlineStr">
         <is>
           <t>2026-3 A</t>
         </is>
       </c>
-      <c r="N16" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O16" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P16" s="12" t="inlineStr">
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4129,76 +4065,76 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>G-14</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Ingeniería de Software</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>2024-1</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Acta pendiente o no enviada</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>SEMINARIO</t>
         </is>
       </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO I</t>
         </is>
       </c>
-      <c r="K18" s="12" t="inlineStr">
+      <c r="K18" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO II</t>
         </is>
       </c>
-      <c r="L18" s="12" t="inlineStr">
+      <c r="L18" s="11" t="inlineStr">
         <is>
           <t>Matriculado</t>
         </is>
       </c>
-      <c r="M18" s="12" t="inlineStr">
+      <c r="M18" s="11" t="inlineStr">
         <is>
           <t>2026-3 I</t>
         </is>
       </c>
-      <c r="N18" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O18" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P18" s="12" t="inlineStr">
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4281,76 +4217,76 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>G-16</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Ingeniería de Software</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>2025-1</t>
         </is>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Aceptó</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>SEMINARIO</t>
         </is>
       </c>
-      <c r="J20" s="12" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO I</t>
         </is>
       </c>
-      <c r="K20" s="12" t="inlineStr">
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO II</t>
         </is>
       </c>
-      <c r="L20" s="12" t="inlineStr">
+      <c r="L20" s="11" t="inlineStr">
         <is>
           <t>Matriculado</t>
         </is>
       </c>
-      <c r="M20" s="12" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr">
         <is>
           <t>2026-3 A</t>
         </is>
       </c>
-      <c r="N20" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O20" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P20" s="12" t="inlineStr">
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O20" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P20" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4433,76 +4369,76 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>G-18</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Ingeniería de Software</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>2025-1</t>
         </is>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="D22" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="F22" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Aceptó</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">SEMINARIO </t>
         </is>
       </c>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO I</t>
         </is>
       </c>
-      <c r="K22" s="12" t="inlineStr">
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>TRABAJO DE GRADO II</t>
         </is>
       </c>
-      <c r="L22" s="12" t="inlineStr">
+      <c r="L22" s="11" t="inlineStr">
         <is>
           <t>Matriculado</t>
         </is>
       </c>
-      <c r="M22" s="12" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr">
         <is>
           <t>2026-3 I</t>
         </is>
       </c>
-      <c r="N22" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O22" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P22" s="12" t="inlineStr">
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O22" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P22" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4540,121 +4476,121 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Matriculado</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>2026-3 I</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>G-20</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Geomática</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>2025-1</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>Aceptó</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>SEMINARIO</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>TRABAJO DE GRADO I</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>TRABAJO DE GRADO II</t>
+        </is>
+      </c>
+      <c r="L24" s="11" t="inlineStr">
         <is>
           <t>Matriculado</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>2026-3 I</t>
-        </is>
-      </c>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O23" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>G-20</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Geomática</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>2025-1</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>2026-3 A</t>
+        </is>
+      </c>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O24" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>SEMINARIO</t>
-        </is>
-      </c>
-      <c r="J24" s="12" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO I</t>
-        </is>
-      </c>
-      <c r="K24" s="12" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO II</t>
-        </is>
-      </c>
-      <c r="L24" s="12" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="M24" s="12" t="inlineStr">
-        <is>
-          <t>2026-3 A</t>
-        </is>
-      </c>
-      <c r="N24" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O24" s="12" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="P24" s="12" t="inlineStr">
+      <c r="P24" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4737,76 +4673,76 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>G-22</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Ingeniería de Software</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>2025-3</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>Acta pendiente o no enviada</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>SEMINARIO</t>
         </is>
       </c>
-      <c r="J26" s="12" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K26" s="12" t="inlineStr">
+      <c r="K26" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="L26" s="11" t="inlineStr">
         <is>
           <t>Matriculado</t>
         </is>
       </c>
-      <c r="M26" s="12" t="inlineStr">
+      <c r="M26" s="11" t="inlineStr">
         <is>
           <t>2026-3 A</t>
         </is>
       </c>
-      <c r="N26" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O26" s="12" t="inlineStr">
+      <c r="N26" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O26" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P26" s="12" t="inlineStr">
+      <c r="P26" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -4853,27 +4789,27 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Número</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Expedida por</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Enlace</t>
         </is>
@@ -4896,30 +4832,30 @@
           <t>Consejo Superior Universitario</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Ver norma</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Resolución</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Consejo Académico</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Ver norma</t>
         </is>
@@ -4942,30 +4878,30 @@
           <t>Consejo Académico</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Ver norma</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Resolución</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Vicerrectoría Académica</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Ver norma</t>
         </is>
@@ -4988,30 +4924,30 @@
           <t>Vicerrectoría Académica</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Ver norma</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Resolución</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Vicerrectoría Académica</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Ver norma</t>
         </is>
@@ -5034,30 +4970,30 @@
           <t>Consejo Superior Universitario</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Ver norma</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Resolución</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="11" t="n">
         <v>48</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Consejo Académico</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Ver norma</t>
         </is>
@@ -5080,7 +5016,7 @@
           <t>Vicerrectoría Académica</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Ver norma</t>
         </is>
@@ -5113,93 +5049,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Diferencias entre fuentes por revisar</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
+          <t>Reunión de acompañamiento académico (06/04/2026, 7:00 p. m., virtual)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Los registros se identifican con su ID; no se corrigió ninguna fuente.</t>
+          <t>Convocatoria de la coordinación a estudiantes cuyo tiempo de permanencia vence en 2026-1, para orientar rutas de culminación del trabajo de grado.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Registro</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Tema</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Detalle</t>
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Modalidad</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Estudiantes convocados</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Fuente</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>P2-05</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Aval de anteproyecto</t>
-        </is>
+          <t>Investigación</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>18</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>El cuadro registra «NO» en viabilidad del aval; revisar antes de presentar.</t>
+          <t>Correo de convocatoria de la coordinación (6 de abril de 2026)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>P2-05</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Fecha de aval</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>La fecha del aval (17/10/2015) es anterior al ingreso; probable error de digitación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>PAGOT</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Modalidad</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>7 estudiantes con plan vigente de Profundización en el archivo de PAGOT figuran como Investigación en las bases MCIC.</t>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Correo de convocatoria de la coordinación (6 de abril de 2026)</t>
         </is>
       </c>
     </row>
@@ -5213,90 +5128,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Reunión de acompañamiento académico (06/04/2026, 7:00 p. m., virtual)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Convocatoria de la coordinación a estudiantes cuyo tiempo de permanencia vence en 2026-1, para orientar rutas de culminación del trabajo de grado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Modalidad</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Estudiantes convocados</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Investigación</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Correo de convocatoria de la coordinación (6 de abril de 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Correo de convocatoria de la coordinación (6 de abril de 2026)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5329,37 +5160,37 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Modalidad</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>

--- a/NuevaData/Presentacion/Investigacion/FACTOR 6. PERMANENCIA Y GRADUACIÓN/d. Seguimiento al avance de trabajos de grado y tiempos de permanencia/F6_Permanencia_y_Graduacion_Investigacion.xlsx
+++ b/NuevaData/Presentacion/Investigacion/FACTOR 6. PERMANENCIA Y GRADUACIÓN/d. Seguimiento al avance de trabajos de grado y tiempos de permanencia/F6_Permanencia_y_Graduacion_Investigacion.xlsx
@@ -8,17 +8,15 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solicitudes de prórroga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAGOT" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seguimiento PAGOT 2026-3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normativa PAGOT" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acompañamiento" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graduados" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lectura de los datos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solicitudes de prórroga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normativa PAGOT" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acompañamiento" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graduados" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Solicitudes de prórroga'!$A$4:$M$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Seguimiento PAGOT 2026-3'!$A$4:$P$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Normativa PAGOT'!$A$4:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Solicitudes de prórroga'!$A$4:$M$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Normativa PAGOT'!$A$4:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -573,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -664,108 +662,193 @@
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Solicitudes de prórroga radicadas 2026-3</t>
+          <t>Estudiantes que solicitaron prórroga 2026-3</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Estudiantes que solicitaron prórroga</t>
+          <t>Solicitantes que son PAGOT (2024-1 a 2025-3)</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Solicitantes que son PAGOT</t>
+          <t>Inscritos oficiales PAGOT 2024-1 a 2025-3</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>PAGOT en seguimiento 2026-3</t>
+          <t>Graduados 2022-2026</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>PAGOT que pagaron la matrícula 2026-3</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Inscritos oficiales PAGOT</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Convocados a acompañamiento</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Graduados 2022-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="G13" s="9" t="n">
         <v>97</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A6:B6"/>
+  <mergeCells count="17">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C6:H6"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="G9:H9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lectura de los datos — Investigación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Cifras agregadas, verificables en Cóndor y en el cuadro de prórrogas 2026-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Graduados 2022-2026</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Máximo anual: 26 en 2022; promedio 2022-2025: 23 por año. Año estimado por la última matrícula en Cóndor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Estudiantes que perdieron la calidad de estudiante (plan vigente 595)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Ingresaron en 2016 o 2017: 8; ingresaron en 2024 o 2026: 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Solicitudes de prórroga 2026-3 con tesis o trabajo de grado radicado</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>De 27 solicitudes (una estudiante radicó en dos rondas; 26 estudiantes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Solicitudes con producto de divulgación</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>14 ponencias en LoHacemosxTIC 2026; 9 ponencias en otros eventos; 4 artículos sometidos a revistas</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Inscritos oficiales a PAGOT (2024-1 a 2025-3)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Por periodo de inscripción: 2024-1: 4; 2025-1: 22; 2025-3: 4.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2635,2130 +2718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="64" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Estudiantes PAGOT — Investigación</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Cruce de las cuatro fuentes disponibles y seguimiento individual 2026-3 (anónimo).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Cruce de fuentes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>Estudiantes</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>También en seguimiento 2026-3</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>También solicitó prórroga 2026-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Base MCIC (columna «Tipo de estudiante» = PAGOT)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Inscritos oficiales a PAGOT 2024-1 a 2025-3 (listado de aspirantes)</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Seguimiento PAGOT 2026-3 (Plan vigente 595)</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    de ellos, pagaron la matrícula 2026-3 (recibo activo)</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Solicitudes de prórroga 2026-3 de estudiantes PAGOT</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Respuesta a la convocatoria de PAGOT (seguimiento 2026-3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Respuesta</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Estudiantes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Acta pendiente o no enviada</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>No respondió</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Otra respuesta</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Estado en Cóndor (seguimiento 2026-3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Estudiantes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>Sin dato de estado</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>En renovación de matrícula - Vacaciones</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Pérdida de calidad de estudiante - Suspendido</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Inscritos oficiales a PAGOT por periodo</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>Periodo</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Estudiantes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>2024-1</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>2025-1</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>2025-3</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A2:P2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Seguimiento individual PAGOT 2026-3 — Investigación</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Un registro por estudiante con ID interno (G-01…); sin nombre, documento ni código. El plan de trabajo son los espacios que cursará cada estudiante en cada periodo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Énfasis (plan de ingreso)</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Último periodo activo</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Créditos aprobados</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Periodos</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Matrículas</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>Respuesta a la convocatoria</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>Pago 2026-3</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>Plan 2026-3</t>
-        </is>
-      </c>
-      <c r="J4" s="10" t="inlineStr">
-        <is>
-          <t>Plan 2027-1</t>
-        </is>
-      </c>
-      <c r="K4" s="10" t="inlineStr">
-        <is>
-          <t>Plan 2027-3</t>
-        </is>
-      </c>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>Estado en Cóndor</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr">
-        <is>
-          <t>Último recibo</t>
-        </is>
-      </c>
-      <c r="N4" s="10" t="inlineStr">
-        <is>
-          <t>Solicitó prórroga 2026-3</t>
-        </is>
-      </c>
-      <c r="O4" s="10" t="inlineStr">
-        <is>
-          <t>En base MCIC como PAGOT</t>
-        </is>
-      </c>
-      <c r="P4" s="10" t="inlineStr">
-        <is>
-          <t>Inscrito oficial PAGOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>G-01</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>2019-2</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>SEMINARIO</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO I</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO II</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>En renovación de matrícula - Vacaciones</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>2026-3 A</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>G-02</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Teleinformática</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>2020-1</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>SEMINARIO</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO I</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO II</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>En renovación de matrícula - Vacaciones</t>
-        </is>
-      </c>
-      <c r="M6" s="11" t="inlineStr">
-        <is>
-          <t>2026-3 A</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="P6" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>G-03</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>2021-2</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>SEMINARIO</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO I</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO II</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>2026-3 A</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>G-04</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Geomática</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>2021-3</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>Acta pendiente o no enviada</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O8" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P8" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>G-05</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>2021-3</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>SEMINARIO</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO I</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO II</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>2026-3 A</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>G-06</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>2021-3 *</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>SEMINARIO</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO I</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO II</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>En renovación de matrícula - Vacaciones</t>
-        </is>
-      </c>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>2026-3 A</t>
-        </is>
-      </c>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O10" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P10" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>G-07</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Geomática</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>2021-I Terminación de materias, 2025-III periodo activo solo por renovacion sin tesis II</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Otra respuesta</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>2026-3 A</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>G-08</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Teleinformática</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O12" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P12" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>G-09</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>2023-2</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>Pérdida de calidad de estudiante - Suspendido</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>2025-3 A</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O13" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>G-10</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>2023-3</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>SEMINARIO</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO I / COMPUTACIÓN PARALELA</t>
-        </is>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO II</t>
-        </is>
-      </c>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="M14" s="11" t="inlineStr">
-        <is>
-          <t>2026-3 A</t>
-        </is>
-      </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O14" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>G-11</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>2023-II</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>No respondió</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>SEMINARIO</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>2026-3 A</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O15" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>G-12</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>2024-1</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>SEMINARIO</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO I</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO II</t>
-        </is>
-      </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="M16" s="11" t="inlineStr">
-        <is>
-          <t>2026-3 A</t>
-        </is>
-      </c>
-      <c r="N16" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O16" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P16" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>G-13</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Teleinformática</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>2024-1</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Acta pendiente o no enviada</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O17" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>G-14</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>2024-1</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Acta pendiente o no enviada</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>SEMINARIO</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO I</t>
-        </is>
-      </c>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO II</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="M18" s="11" t="inlineStr">
-        <is>
-          <t>2026-3 I</t>
-        </is>
-      </c>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O18" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P18" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>G-15</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>2024-3</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>No respondió</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O19" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>G-16</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>2025-1</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>SEMINARIO</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO I</t>
-        </is>
-      </c>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO II</t>
-        </is>
-      </c>
-      <c r="L20" s="11" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="M20" s="11" t="inlineStr">
-        <is>
-          <t>2026-3 A</t>
-        </is>
-      </c>
-      <c r="N20" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O20" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P20" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>G-17</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Teleinformática</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>2025-1</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>No respondió</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M21" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N21" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O21" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>G-18</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>2025-1</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEMINARIO </t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO I</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO II</t>
-        </is>
-      </c>
-      <c r="L22" s="11" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="M22" s="11" t="inlineStr">
-        <is>
-          <t>2026-3 I</t>
-        </is>
-      </c>
-      <c r="N22" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O22" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P22" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>G-19</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>2025-1</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>2026-3 I</t>
-        </is>
-      </c>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O23" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>G-20</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Geomática</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>2025-1</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>SEMINARIO</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO I</t>
-        </is>
-      </c>
-      <c r="K24" s="11" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO II</t>
-        </is>
-      </c>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="M24" s="11" t="inlineStr">
-        <is>
-          <t>2026-3 A</t>
-        </is>
-      </c>
-      <c r="N24" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O24" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="P24" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>G-21</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Geomática</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>2025-3</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>Aceptó</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>SEMINARIO / ESTADÍSTICA ESPACIAL</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRABAJO DE GRADO I </t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>TRABAJO DE GRADO II</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="M25" s="6" t="inlineStr">
-        <is>
-          <t>2026-3 A</t>
-        </is>
-      </c>
-      <c r="N25" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O25" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>G-22</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>Ingeniería de Software</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>2025-3</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>Acta pendiente o no enviada</t>
-        </is>
-      </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>SEMINARIO</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K26" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L26" s="11" t="inlineStr">
-        <is>
-          <t>Matriculado</t>
-        </is>
-      </c>
-      <c r="M26" s="11" t="inlineStr">
-        <is>
-          <t>2026-3 A</t>
-        </is>
-      </c>
-      <c r="N26" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O26" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="P26" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:P26"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5043,7 +3003,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5127,7 +3087,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
